--- a/Ejercicios.xlsx
+++ b/Ejercicios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josev\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTUDIANTES\Downloads\MisEjercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58622BB9-387A-4646-9040-BE1618843683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC11D70B-51A7-4DC0-8200-978832FB5D95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="867" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enunciados" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,12 @@
     <sheet name="E9_Panel" sheetId="11" r:id="rId11"/>
     <sheet name="E10_Credito" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="356">
   <si>
     <t>Recuperación – Excel</t>
   </si>
@@ -1105,13 +1105,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1164,6 +1165,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1231,7 +1238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1266,21 +1273,22 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1964,9 +1972,18 @@
       <c r="E5" s="18">
         <v>46128</v>
       </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="27">
+        <f>WORKDAY(C5,D5,Festivos!$A$5:$A$22)</f>
+        <v>46127</v>
+      </c>
+      <c r="G5" s="19">
+        <f>IF(E5="","",NETWORKDAYS(C5,E5,Festivos!$A$5:$A$22)-1)</f>
+        <v>8</v>
+      </c>
+      <c r="H5" s="19" t="str">
+        <f>IF(E5="","Pendiente",IF(E5&gt;F5,"Retrasado","A tiempo"))</f>
+        <v>Retrasado</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="7" t="s">
         <v>99</v>
@@ -1991,14 +2008,26 @@
       <c r="E6" s="18">
         <v>46170</v>
       </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="F6" s="27">
+        <f>WORKDAY(C6,D6,Festivos!$A$5:$A$22)</f>
+        <v>46170</v>
+      </c>
+      <c r="G6" s="19">
+        <f>IF(E6="","",NETWORKDAYS(C6,E6,Festivos!$A$5:$A$22)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="H6" s="19" t="str">
+        <f t="shared" ref="H6:H22" si="0">IF(E6="","Pendiente",IF(E6&gt;F6,"Retrasado","A tiempo"))</f>
+        <v>A tiempo</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="K6" s="19"/>
+      <c r="K6" s="19">
+        <f>COUNTIFS($B$5:$B$22,J6,$H$5:$H$22,"Retrasado")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -2016,14 +2045,26 @@
       <c r="E7" s="18">
         <v>46120</v>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="27">
+        <f>WORKDAY(C7,D7,Festivos!$A$5:$A$22)</f>
+        <v>46118</v>
+      </c>
+      <c r="G7" s="19">
+        <f>IF(E7="","",NETWORKDAYS(C7,E7,Festivos!$A$5:$A$22)-1)</f>
+        <v>5</v>
+      </c>
+      <c r="H7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="K7" s="19"/>
+      <c r="K7" s="19">
+        <f t="shared" ref="K7:K9" si="1">COUNTIFS($B$5:$B$22,J7,$H$5:$H$22,"Retrasado")</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
@@ -2041,14 +2082,26 @@
       <c r="E8" s="18">
         <v>46131</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="27">
+        <f>WORKDAY(C8,D8,Festivos!$A$5:$A$22)</f>
+        <v>46127</v>
+      </c>
+      <c r="G8" s="19">
+        <f>IF(E8="","",NETWORKDAYS(C8,E8,Festivos!$A$5:$A$22)-1)</f>
+        <v>4</v>
+      </c>
+      <c r="H8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="K8" s="19"/>
+      <c r="K8" s="19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
@@ -2064,14 +2117,26 @@
         <v>3</v>
       </c>
       <c r="E9" s="18"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
+      <c r="F9" s="27">
+        <f>WORKDAY(C9,D9,Festivos!$A$5:$A$22)</f>
+        <v>46139</v>
+      </c>
+      <c r="G9" s="19" t="str">
+        <f>IF(E9="","",NETWORKDAYS(C9,E9,Festivos!$A$5:$A$22)-1)</f>
+        <v/>
+      </c>
+      <c r="H9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Pendiente</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="K9" s="19"/>
+      <c r="K9" s="19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -2089,9 +2154,18 @@
       <c r="E10" s="18">
         <v>46142</v>
       </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
+      <c r="F10" s="27">
+        <f>WORKDAY(C10,D10,Festivos!$A$5:$A$22)</f>
+        <v>46142</v>
+      </c>
+      <c r="G10" s="19">
+        <f>IF(E10="","",NETWORKDAYS(C10,E10,Festivos!$A$5:$A$22)-1)</f>
+        <v>8</v>
+      </c>
+      <c r="H10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>A tiempo</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2112,9 +2186,18 @@
       <c r="E11" s="18">
         <v>46156</v>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
+      <c r="F11" s="27">
+        <f>WORKDAY(C11,D11,Festivos!$A$5:$A$22)</f>
+        <v>46155</v>
+      </c>
+      <c r="G11" s="19">
+        <f>IF(E11="","",NETWORKDAYS(C11,E11,Festivos!$A$5:$A$22)-1)</f>
+        <v>9</v>
+      </c>
+      <c r="H11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2135,9 +2218,18 @@
       <c r="E12" s="18">
         <v>46170</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
+      <c r="F12" s="27">
+        <f>WORKDAY(C12,D12,Festivos!$A$5:$A$22)</f>
+        <v>46170</v>
+      </c>
+      <c r="G12" s="19">
+        <f>IF(E12="","",NETWORKDAYS(C12,E12,Festivos!$A$5:$A$22)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="H12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>A tiempo</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2158,9 +2250,18 @@
       <c r="E13" s="18">
         <v>46124</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="27">
+        <f>WORKDAY(C13,D13,Festivos!$A$5:$A$22)</f>
+        <v>46122</v>
+      </c>
+      <c r="G13" s="19">
+        <f>IF(E13="","",NETWORKDAYS(C13,E13,Festivos!$A$5:$A$22)-1)</f>
+        <v>2</v>
+      </c>
+      <c r="H13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2181,9 +2282,18 @@
       <c r="E14" s="18">
         <v>46124</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
+      <c r="F14" s="27">
+        <f>WORKDAY(C14,D14,Festivos!$A$5:$A$22)</f>
+        <v>46127</v>
+      </c>
+      <c r="G14" s="19">
+        <f>IF(E14="","",NETWORKDAYS(C14,E14,Festivos!$A$5:$A$22)-1)</f>
+        <v>4</v>
+      </c>
+      <c r="H14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>A tiempo</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2204,9 +2314,18 @@
       <c r="E15" s="18">
         <v>46148</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="F15" s="27">
+        <f>WORKDAY(C15,D15,Festivos!$A$5:$A$22)</f>
+        <v>46150</v>
+      </c>
+      <c r="G15" s="19">
+        <f>IF(E15="","",NETWORKDAYS(C15,E15,Festivos!$A$5:$A$22)-1)</f>
+        <v>6</v>
+      </c>
+      <c r="H15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>A tiempo</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2225,9 +2344,18 @@
         <v>3</v>
       </c>
       <c r="E16" s="18"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="F16" s="27">
+        <f>WORKDAY(C16,D16,Festivos!$A$5:$A$22)</f>
+        <v>46133</v>
+      </c>
+      <c r="G16" s="19" t="str">
+        <f>IF(E16="","",NETWORKDAYS(C16,E16,Festivos!$A$5:$A$22)-1)</f>
+        <v/>
+      </c>
+      <c r="H16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Pendiente</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2248,9 +2376,18 @@
       <c r="E17" s="18">
         <v>46113</v>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
+      <c r="F17" s="27">
+        <f>WORKDAY(C17,D17,Festivos!$A$5:$A$22)</f>
+        <v>46106</v>
+      </c>
+      <c r="G17" s="19">
+        <f>IF(E17="","",NETWORKDAYS(C17,E17,Festivos!$A$5:$A$22)-1)</f>
+        <v>6</v>
+      </c>
+      <c r="H17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2271,9 +2408,18 @@
       <c r="E18" s="18">
         <v>46118</v>
       </c>
-      <c r="F18" s="27"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+      <c r="F18" s="27">
+        <f>WORKDAY(C18,D18,Festivos!$A$5:$A$22)</f>
+        <v>46119</v>
+      </c>
+      <c r="G18" s="19">
+        <f>IF(E18="","",NETWORKDAYS(C18,E18,Festivos!$A$5:$A$22)-1)</f>
+        <v>7</v>
+      </c>
+      <c r="H18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>A tiempo</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -2294,9 +2440,18 @@
       <c r="E19" s="18">
         <v>46147</v>
       </c>
-      <c r="F19" s="27"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="F19" s="27">
+        <f>WORKDAY(C19,D19,Festivos!$A$5:$A$22)</f>
+        <v>46142</v>
+      </c>
+      <c r="G19" s="19">
+        <f>IF(E19="","",NETWORKDAYS(C19,E19,Festivos!$A$5:$A$22)-1)</f>
+        <v>10</v>
+      </c>
+      <c r="H19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2317,9 +2472,18 @@
       <c r="E20" s="18">
         <v>46171</v>
       </c>
-      <c r="F20" s="27"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
+      <c r="F20" s="27">
+        <f>WORKDAY(C20,D20,Festivos!$A$5:$A$22)</f>
+        <v>46170</v>
+      </c>
+      <c r="G20" s="19">
+        <f>IF(E20="","",NETWORKDAYS(C20,E20,Festivos!$A$5:$A$22)-1)</f>
+        <v>6</v>
+      </c>
+      <c r="H20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2338,9 +2502,18 @@
         <v>8</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
+      <c r="F21" s="27">
+        <f>WORKDAY(C21,D21,Festivos!$A$5:$A$22)</f>
+        <v>46127</v>
+      </c>
+      <c r="G21" s="19" t="str">
+        <f>IF(E21="","",NETWORKDAYS(C21,E21,Festivos!$A$5:$A$22)-1)</f>
+        <v/>
+      </c>
+      <c r="H21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Pendiente</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -2361,9 +2534,18 @@
       <c r="E22" s="18">
         <v>46160</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
+      <c r="F22" s="27">
+        <f>WORKDAY(C22,D22,Festivos!$A$5:$A$22)</f>
+        <v>46157</v>
+      </c>
+      <c r="G22" s="19">
+        <f>IF(E22="","",NETWORKDAYS(C22,E22,Festivos!$A$5:$A$22)-1)</f>
+        <v>8</v>
+      </c>
+      <c r="H22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Retrasado</v>
+      </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -2416,7 +2598,10 @@
       <c r="A7" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="B7" s="20"/>
+      <c r="B7" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$C$5:$C$84,$B$4,Ventas!$B$5:$B$84,"&gt;="&amp;DATE(2026,$B$5,1),Ventas!$B$5:$B$84,"&lt;"&amp;DATE(2026,$B$5+1,1))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
@@ -2532,7 +2717,10 @@
       <c r="A6" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="B6" s="30"/>
+      <c r="B6" s="30">
+        <f>(1+B4)^(1/12)-1</f>
+        <v>1.8429051189551959E-2</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -2544,7 +2732,10 @@
       <c r="A7" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="B7" s="20"/>
+      <c r="B7" s="31">
+        <f>PMT(B6,B5,-B3)</f>
+        <v>956247.50226178591</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -3072,6 +3263,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3575,9 +3767,18 @@
       <c r="F5" s="14">
         <v>5</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="G5" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E5,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H5" s="20">
+        <f>IFERROR(VLOOKUP(E5,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I5" s="20">
+        <f>IFERROR(F5*H5*(1-VLOOKUP(VLOOKUP(E5,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>725000</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
@@ -3598,9 +3799,18 @@
       <c r="F6" s="14">
         <v>2</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
+      <c r="G6" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E6,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Portátil 16"</v>
+      </c>
+      <c r="H6" s="20">
+        <f>IFERROR(VLOOKUP(E6,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>4550000</v>
+      </c>
+      <c r="I6" s="20">
+        <f>IFERROR(F6*H6*(1-VLOOKUP(VLOOKUP(E6,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>8190000</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -3621,9 +3831,18 @@
       <c r="F7" s="14">
         <v>4</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
+      <c r="G7" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E7,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H7" s="20">
+        <f>IFERROR(VLOOKUP(E7,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I7" s="20">
+        <f>IFERROR(F7*H7*(1-VLOOKUP(VLOOKUP(E7,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>225040</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
@@ -3644,9 +3863,18 @@
       <c r="F8" s="14">
         <v>4</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
+      <c r="G8" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E8,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Portátil 14"</v>
+      </c>
+      <c r="H8" s="20">
+        <f>IFERROR(VLOOKUP(E8,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>3200000</v>
+      </c>
+      <c r="I8" s="20">
+        <f>IFERROR(F8*H8*(1-VLOOKUP(VLOOKUP(E8,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>11520000</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
@@ -3667,9 +3895,18 @@
       <c r="F9" s="14">
         <v>5</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
+      <c r="G9" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E9,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Disco SSD 1TB</v>
+      </c>
+      <c r="H9" s="20">
+        <f>IFERROR(VLOOKUP(E9,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>390000</v>
+      </c>
+      <c r="I9" s="20">
+        <f>IFERROR(F9*H9*(1-VLOOKUP(VLOOKUP(E9,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1891500</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -3690,9 +3927,18 @@
       <c r="F10" s="14">
         <v>1</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
+      <c r="G10" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E10,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Disco SSD 1TB</v>
+      </c>
+      <c r="H10" s="20">
+        <f>IFERROR(VLOOKUP(E10,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>390000</v>
+      </c>
+      <c r="I10" s="20">
+        <f>IFERROR(F10*H10*(1-VLOOKUP(VLOOKUP(E10,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>378300</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
@@ -3713,9 +3959,18 @@
       <c r="F11" s="14">
         <v>5</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
+      <c r="G11" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E11,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Teclado mecánico</v>
+      </c>
+      <c r="H11" s="20">
+        <f>IFERROR(VLOOKUP(E11,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>185000</v>
+      </c>
+      <c r="I11" s="20">
+        <f>IFERROR(F11*H11*(1-VLOOKUP(VLOOKUP(E11,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>878750</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
@@ -3736,9 +3991,18 @@
       <c r="F12" s="14">
         <v>4</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
+      <c r="G12" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E12,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Portátil 14"</v>
+      </c>
+      <c r="H12" s="20">
+        <f>IFERROR(VLOOKUP(E12,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>3200000</v>
+      </c>
+      <c r="I12" s="20">
+        <f>IFERROR(F12*H12*(1-VLOOKUP(VLOOKUP(E12,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>11520000</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
@@ -3759,9 +4023,18 @@
       <c r="F13" s="14">
         <v>4</v>
       </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
+      <c r="G13" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E13,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H13" s="20">
+        <f>IFERROR(VLOOKUP(E13,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I13" s="20">
+        <f>IFERROR(F13*H13*(1-VLOOKUP(VLOOKUP(E13,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>920000</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
@@ -3782,9 +4055,18 @@
       <c r="F14" s="14">
         <v>2</v>
       </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
+      <c r="G14" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E14,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H14" s="20">
+        <f>IFERROR(VLOOKUP(E14,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I14" s="20">
+        <f>IFERROR(F14*H14*(1-VLOOKUP(VLOOKUP(E14,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1269600</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
@@ -3805,9 +4087,18 @@
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
+      <c r="G15" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E15,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H15" s="20">
+        <f>IFERROR(VLOOKUP(E15,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I15" s="20">
+        <f>IFERROR(F15*H15*(1-VLOOKUP(VLOOKUP(E15,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1269600</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
@@ -3828,9 +4119,18 @@
       <c r="F16" s="14">
         <v>6</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="G16" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E16,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H16" s="20">
+        <f>IFERROR(VLOOKUP(E16,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I16" s="20">
+        <f>IFERROR(F16*H16*(1-VLOOKUP(VLOOKUP(E16,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>337560</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
@@ -3851,9 +4151,18 @@
       <c r="F17" s="14">
         <v>2</v>
       </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
+      <c r="G17" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E17,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H17" s="20">
+        <f>IFERROR(VLOOKUP(E17,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I17" s="20">
+        <f>IFERROR(F17*H17*(1-VLOOKUP(VLOOKUP(E17,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>290000</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
@@ -3874,9 +4183,18 @@
       <c r="F18" s="14">
         <v>6</v>
       </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
+      <c r="G18" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E18,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Cámara web HD</v>
+      </c>
+      <c r="H18" s="20">
+        <f>IFERROR(VLOOKUP(E18,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>165000</v>
+      </c>
+      <c r="I18" s="20">
+        <f>IFERROR(F18*H18*(1-VLOOKUP(VLOOKUP(E18,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>940500</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
@@ -3897,9 +4215,18 @@
       <c r="F19" s="14">
         <v>6</v>
       </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="G19" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E19,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H19" s="20">
+        <f>IFERROR(VLOOKUP(E19,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I19" s="20">
+        <f>IFERROR(F19*H19*(1-VLOOKUP(VLOOKUP(E19,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>337560</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
@@ -3920,9 +4247,18 @@
       <c r="F20" s="14">
         <v>5</v>
       </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
+      <c r="G20" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E20,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Mouse inalámbrico</v>
+      </c>
+      <c r="H20" s="20">
+        <f>IFERROR(VLOOKUP(E20,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>72000</v>
+      </c>
+      <c r="I20" s="20">
+        <f>IFERROR(F20*H20*(1-VLOOKUP(VLOOKUP(E20,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>342000</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
@@ -3943,9 +4279,18 @@
       <c r="F21" s="14">
         <v>2</v>
       </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="G21" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E21,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Teclado mecánico</v>
+      </c>
+      <c r="H21" s="20">
+        <f>IFERROR(VLOOKUP(E21,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>185000</v>
+      </c>
+      <c r="I21" s="20">
+        <f>IFERROR(F21*H21*(1-VLOOKUP(VLOOKUP(E21,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>351500</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
@@ -3966,9 +4311,18 @@
       <c r="F22" s="14">
         <v>5</v>
       </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
+      <c r="G22" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E22,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Mouse inalámbrico</v>
+      </c>
+      <c r="H22" s="20">
+        <f>IFERROR(VLOOKUP(E22,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>72000</v>
+      </c>
+      <c r="I22" s="20">
+        <f>IFERROR(F22*H22*(1-VLOOKUP(VLOOKUP(E22,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>342000</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
@@ -3989,9 +4343,18 @@
       <c r="F23" s="14">
         <v>6</v>
       </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="G23" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E23,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>CÓDIGO NO EXISTE</v>
+      </c>
+      <c r="H23" s="20">
+        <f>IFERROR(VLOOKUP(E23,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="20">
+        <f>IFERROR(F23*H23*(1-VLOOKUP(VLOOKUP(E23,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
@@ -4012,9 +4375,18 @@
       <c r="F24" s="14">
         <v>4</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
+      <c r="G24" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E24,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H24" s="20">
+        <f>IFERROR(VLOOKUP(E24,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I24" s="20">
+        <f>IFERROR(F24*H24*(1-VLOOKUP(VLOOKUP(E24,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>2539200</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
@@ -4035,9 +4407,18 @@
       <c r="F25" s="14">
         <v>3</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
+      <c r="G25" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E25,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H25" s="20">
+        <f>IFERROR(VLOOKUP(E25,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I25" s="20">
+        <f>IFERROR(F25*H25*(1-VLOOKUP(VLOOKUP(E25,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>690000</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
@@ -4058,9 +4439,18 @@
       <c r="F26" s="14">
         <v>5</v>
       </c>
-      <c r="G26" s="19"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
+      <c r="G26" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E26,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Cámara web HD</v>
+      </c>
+      <c r="H26" s="20">
+        <f>IFERROR(VLOOKUP(E26,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>165000</v>
+      </c>
+      <c r="I26" s="20">
+        <f>IFERROR(F26*H26*(1-VLOOKUP(VLOOKUP(E26,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>783750</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
@@ -4081,9 +4471,18 @@
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
+      <c r="G27" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E27,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H27" s="20">
+        <f>IFERROR(VLOOKUP(E27,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I27" s="20">
+        <f>IFERROR(F27*H27*(1-VLOOKUP(VLOOKUP(E27,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>290000</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
@@ -4104,9 +4503,18 @@
       <c r="F28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
+      <c r="G28" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E28,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Mouse inalámbrico</v>
+      </c>
+      <c r="H28" s="20">
+        <f>IFERROR(VLOOKUP(E28,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>72000</v>
+      </c>
+      <c r="I28" s="20">
+        <f>IFERROR(F28*H28*(1-VLOOKUP(VLOOKUP(E28,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>273600</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
@@ -4127,9 +4535,18 @@
       <c r="F29" s="14">
         <v>6</v>
       </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
+      <c r="G29" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E29,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H29" s="20">
+        <f>IFERROR(VLOOKUP(E29,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I29" s="20">
+        <f>IFERROR(F29*H29*(1-VLOOKUP(VLOOKUP(E29,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>3808800</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
@@ -4150,9 +4567,18 @@
       <c r="F30" s="14">
         <v>5</v>
       </c>
-      <c r="G30" s="19"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="G30" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E30,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Disco SSD 1TB</v>
+      </c>
+      <c r="H30" s="20">
+        <f>IFERROR(VLOOKUP(E30,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>390000</v>
+      </c>
+      <c r="I30" s="20">
+        <f>IFERROR(F30*H30*(1-VLOOKUP(VLOOKUP(E30,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1891500</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
@@ -4173,9 +4599,18 @@
       <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
+      <c r="G31" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E31,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>CÓDIGO NO EXISTE</v>
+      </c>
+      <c r="H31" s="20">
+        <f>IFERROR(VLOOKUP(E31,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="20">
+        <f>IFERROR(F31*H31*(1-VLOOKUP(VLOOKUP(E31,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
@@ -4196,9 +4631,18 @@
       <c r="F32" s="14">
         <v>2</v>
       </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
+      <c r="G32" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E32,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Base refrigerante</v>
+      </c>
+      <c r="H32" s="20">
+        <f>IFERROR(VLOOKUP(E32,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>89000</v>
+      </c>
+      <c r="I32" s="20">
+        <f>IFERROR(F32*H32*(1-VLOOKUP(VLOOKUP(E32,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>156640</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
@@ -4207,9 +4651,7 @@
       <c r="B33" s="18">
         <v>46087</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>106</v>
-      </c>
+      <c r="C33" s="14"/>
       <c r="D33" s="14" t="s">
         <v>107</v>
       </c>
@@ -4219,9 +4661,18 @@
       <c r="F33" s="14">
         <v>4</v>
       </c>
-      <c r="G33" s="19"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
+      <c r="G33" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E33,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H33" s="20">
+        <f>IFERROR(VLOOKUP(E33,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I33" s="20">
+        <f>IFERROR(F33*H33*(1-VLOOKUP(VLOOKUP(E33,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>580000</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
@@ -4242,9 +4693,18 @@
       <c r="F34" s="14">
         <v>5</v>
       </c>
-      <c r="G34" s="19"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
+      <c r="G34" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E34,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Base refrigerante</v>
+      </c>
+      <c r="H34" s="20">
+        <f>IFERROR(VLOOKUP(E34,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>89000</v>
+      </c>
+      <c r="I34" s="20">
+        <f>IFERROR(F34*H34*(1-VLOOKUP(VLOOKUP(E34,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>391600</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
@@ -4265,9 +4725,18 @@
       <c r="F35" s="14">
         <v>3</v>
       </c>
-      <c r="G35" s="19"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="G35" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E35,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Cámara web HD</v>
+      </c>
+      <c r="H35" s="20">
+        <f>IFERROR(VLOOKUP(E35,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>165000</v>
+      </c>
+      <c r="I35" s="20">
+        <f>IFERROR(F35*H35*(1-VLOOKUP(VLOOKUP(E35,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>470250</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
@@ -4288,9 +4757,18 @@
       <c r="F36" s="14">
         <v>3</v>
       </c>
-      <c r="G36" s="19"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
+      <c r="G36" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E36,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H36" s="20">
+        <f>IFERROR(VLOOKUP(E36,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I36" s="20">
+        <f>IFERROR(F36*H36*(1-VLOOKUP(VLOOKUP(E36,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>690000</v>
+      </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
@@ -4311,9 +4789,18 @@
       <c r="F37" s="14">
         <v>2</v>
       </c>
-      <c r="G37" s="19"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
+      <c r="G37" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E37,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Cámara web HD</v>
+      </c>
+      <c r="H37" s="20">
+        <f>IFERROR(VLOOKUP(E37,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>165000</v>
+      </c>
+      <c r="I37" s="20">
+        <f>IFERROR(F37*H37*(1-VLOOKUP(VLOOKUP(E37,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>313500</v>
+      </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
@@ -4334,9 +4821,18 @@
       <c r="F38" s="14">
         <v>1</v>
       </c>
-      <c r="G38" s="19"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
+      <c r="G38" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E38,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H38" s="20">
+        <f>IFERROR(VLOOKUP(E38,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I38" s="20">
+        <f>IFERROR(F38*H38*(1-VLOOKUP(VLOOKUP(E38,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>634800</v>
+      </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
@@ -4357,9 +4853,18 @@
       <c r="F39" s="14">
         <v>4</v>
       </c>
-      <c r="G39" s="19"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
+      <c r="G39" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E39,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Cámara web HD</v>
+      </c>
+      <c r="H39" s="20">
+        <f>IFERROR(VLOOKUP(E39,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>165000</v>
+      </c>
+      <c r="I39" s="20">
+        <f>IFERROR(F39*H39*(1-VLOOKUP(VLOOKUP(E39,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>627000</v>
+      </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
@@ -4380,9 +4885,18 @@
       <c r="F40" s="14">
         <v>3</v>
       </c>
-      <c r="G40" s="19"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
+      <c r="G40" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E40,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Base refrigerante</v>
+      </c>
+      <c r="H40" s="20">
+        <f>IFERROR(VLOOKUP(E40,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>89000</v>
+      </c>
+      <c r="I40" s="20">
+        <f>IFERROR(F40*H40*(1-VLOOKUP(VLOOKUP(E40,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>234960</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
@@ -4403,9 +4917,18 @@
       <c r="F41" s="14">
         <v>6</v>
       </c>
-      <c r="G41" s="19"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
+      <c r="G41" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E41,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H41" s="20">
+        <f>IFERROR(VLOOKUP(E41,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I41" s="20">
+        <f>IFERROR(F41*H41*(1-VLOOKUP(VLOOKUP(E41,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>870000</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
@@ -4426,9 +4949,18 @@
       <c r="F42" s="14">
         <v>2</v>
       </c>
-      <c r="G42" s="19"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
+      <c r="G42" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E42,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H42" s="20">
+        <f>IFERROR(VLOOKUP(E42,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I42" s="20">
+        <f>IFERROR(F42*H42*(1-VLOOKUP(VLOOKUP(E42,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>112520</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
@@ -4449,9 +4981,18 @@
       <c r="F43" s="14">
         <v>4</v>
       </c>
-      <c r="G43" s="19"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
+      <c r="G43" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E43,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H43" s="20">
+        <f>IFERROR(VLOOKUP(E43,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I43" s="20">
+        <f>IFERROR(F43*H43*(1-VLOOKUP(VLOOKUP(E43,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>920000</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
@@ -4472,9 +5013,18 @@
       <c r="F44" s="14">
         <v>6</v>
       </c>
-      <c r="G44" s="19"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
+      <c r="G44" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E44,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H44" s="20">
+        <f>IFERROR(VLOOKUP(E44,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I44" s="20">
+        <f>IFERROR(F44*H44*(1-VLOOKUP(VLOOKUP(E44,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1380000</v>
+      </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
@@ -4495,9 +5045,18 @@
       <c r="F45" s="14">
         <v>3</v>
       </c>
-      <c r="G45" s="19"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
+      <c r="G45" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E45,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Base refrigerante</v>
+      </c>
+      <c r="H45" s="20">
+        <f>IFERROR(VLOOKUP(E45,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>89000</v>
+      </c>
+      <c r="I45" s="20">
+        <f>IFERROR(F45*H45*(1-VLOOKUP(VLOOKUP(E45,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>234960</v>
+      </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
@@ -4518,9 +5077,18 @@
       <c r="F46" s="14">
         <v>2</v>
       </c>
-      <c r="G46" s="19"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
+      <c r="G46" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E46,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 27"</v>
+      </c>
+      <c r="H46" s="20">
+        <f>IFERROR(VLOOKUP(E46,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>1150000</v>
+      </c>
+      <c r="I46" s="20">
+        <f>IFERROR(F46*H46*(1-VLOOKUP(VLOOKUP(E46,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>2116000</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
@@ -4541,9 +5109,18 @@
       <c r="F47" s="14">
         <v>1</v>
       </c>
-      <c r="G47" s="19"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
+      <c r="G47" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E47,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Mouse inalámbrico</v>
+      </c>
+      <c r="H47" s="20">
+        <f>IFERROR(VLOOKUP(E47,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>72000</v>
+      </c>
+      <c r="I47" s="20">
+        <f>IFERROR(F47*H47*(1-VLOOKUP(VLOOKUP(E47,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>68400</v>
+      </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
@@ -4564,9 +5141,18 @@
       <c r="F48" s="14">
         <v>1</v>
       </c>
-      <c r="G48" s="19"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
+      <c r="G48" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E48,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 27"</v>
+      </c>
+      <c r="H48" s="20">
+        <f>IFERROR(VLOOKUP(E48,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>1150000</v>
+      </c>
+      <c r="I48" s="20">
+        <f>IFERROR(F48*H48*(1-VLOOKUP(VLOOKUP(E48,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1058000</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
@@ -4587,9 +5173,18 @@
       <c r="F49" s="14">
         <v>1</v>
       </c>
-      <c r="G49" s="19"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
+      <c r="G49" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E49,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Teclado mecánico</v>
+      </c>
+      <c r="H49" s="20">
+        <f>IFERROR(VLOOKUP(E49,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>185000</v>
+      </c>
+      <c r="I49" s="20">
+        <f>IFERROR(F49*H49*(1-VLOOKUP(VLOOKUP(E49,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>175750</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
@@ -4610,9 +5205,18 @@
       <c r="F50" s="14">
         <v>5</v>
       </c>
-      <c r="G50" s="19"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
+      <c r="G50" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E50,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Teclado mecánico</v>
+      </c>
+      <c r="H50" s="20">
+        <f>IFERROR(VLOOKUP(E50,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>185000</v>
+      </c>
+      <c r="I50" s="20">
+        <f>IFERROR(F50*H50*(1-VLOOKUP(VLOOKUP(E50,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>878750</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
@@ -4633,9 +5237,18 @@
       <c r="F51" s="14">
         <v>3</v>
       </c>
-      <c r="G51" s="19"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
+      <c r="G51" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E51,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H51" s="20">
+        <f>IFERROR(VLOOKUP(E51,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I51" s="20">
+        <f>IFERROR(F51*H51*(1-VLOOKUP(VLOOKUP(E51,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>168780</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
@@ -4656,9 +5269,18 @@
       <c r="F52" s="14">
         <v>6</v>
       </c>
-      <c r="G52" s="19"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
+      <c r="G52" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E52,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H52" s="20">
+        <f>IFERROR(VLOOKUP(E52,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I52" s="20">
+        <f>IFERROR(F52*H52*(1-VLOOKUP(VLOOKUP(E52,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1380000</v>
+      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
@@ -4679,9 +5301,18 @@
       <c r="F53" s="14">
         <v>6</v>
       </c>
-      <c r="G53" s="19"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
+      <c r="G53" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E53,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H53" s="20">
+        <f>IFERROR(VLOOKUP(E53,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I53" s="20">
+        <f>IFERROR(F53*H53*(1-VLOOKUP(VLOOKUP(E53,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>870000</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
@@ -4702,9 +5333,18 @@
       <c r="F54" s="14">
         <v>1</v>
       </c>
-      <c r="G54" s="19"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
+      <c r="G54" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E54,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 27"</v>
+      </c>
+      <c r="H54" s="20">
+        <f>IFERROR(VLOOKUP(E54,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>1150000</v>
+      </c>
+      <c r="I54" s="20">
+        <f>IFERROR(F54*H54*(1-VLOOKUP(VLOOKUP(E54,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1058000</v>
+      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
@@ -4725,9 +5365,18 @@
       <c r="F55" s="14">
         <v>2</v>
       </c>
-      <c r="G55" s="19"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
+      <c r="G55" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E55,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>CÓDIGO NO EXISTE</v>
+      </c>
+      <c r="H55" s="20">
+        <f>IFERROR(VLOOKUP(E55,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="20">
+        <f>IFERROR(F55*H55*(1-VLOOKUP(VLOOKUP(E55,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
@@ -4748,9 +5397,18 @@
       <c r="F56" s="14">
         <v>1</v>
       </c>
-      <c r="G56" s="19"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
+      <c r="G56" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E56,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 27"</v>
+      </c>
+      <c r="H56" s="20">
+        <f>IFERROR(VLOOKUP(E56,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>1150000</v>
+      </c>
+      <c r="I56" s="20">
+        <f>IFERROR(F56*H56*(1-VLOOKUP(VLOOKUP(E56,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1058000</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
@@ -4771,9 +5429,18 @@
       <c r="F57" s="14">
         <v>5</v>
       </c>
-      <c r="G57" s="19"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
+      <c r="G57" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E57,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H57" s="20">
+        <f>IFERROR(VLOOKUP(E57,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I57" s="20">
+        <f>IFERROR(F57*H57*(1-VLOOKUP(VLOOKUP(E57,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1150000</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
@@ -4794,9 +5461,18 @@
       <c r="F58" s="14">
         <v>3</v>
       </c>
-      <c r="G58" s="19"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
+      <c r="G58" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E58,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Mouse inalámbrico</v>
+      </c>
+      <c r="H58" s="20">
+        <f>IFERROR(VLOOKUP(E58,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>72000</v>
+      </c>
+      <c r="I58" s="20">
+        <f>IFERROR(F58*H58*(1-VLOOKUP(VLOOKUP(E58,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>205200</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
@@ -4817,9 +5493,18 @@
       <c r="F59" s="14">
         <v>1</v>
       </c>
-      <c r="G59" s="19"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
+      <c r="G59" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E59,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H59" s="20">
+        <f>IFERROR(VLOOKUP(E59,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I59" s="20">
+        <f>IFERROR(F59*H59*(1-VLOOKUP(VLOOKUP(E59,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>56260</v>
+      </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
@@ -4840,9 +5525,18 @@
       <c r="F60" s="14">
         <v>2</v>
       </c>
-      <c r="G60" s="19"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
+      <c r="G60" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E60,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Portátil 14"</v>
+      </c>
+      <c r="H60" s="20">
+        <f>IFERROR(VLOOKUP(E60,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>3200000</v>
+      </c>
+      <c r="I60" s="20">
+        <f>IFERROR(F60*H60*(1-VLOOKUP(VLOOKUP(E60,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>5760000</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
@@ -4863,9 +5557,18 @@
       <c r="F61" s="14">
         <v>1</v>
       </c>
-      <c r="G61" s="19"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
+      <c r="G61" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E61,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Cámara web HD</v>
+      </c>
+      <c r="H61" s="20">
+        <f>IFERROR(VLOOKUP(E61,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>165000</v>
+      </c>
+      <c r="I61" s="20">
+        <f>IFERROR(F61*H61*(1-VLOOKUP(VLOOKUP(E61,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>156750</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
@@ -4886,9 +5589,18 @@
       <c r="F62" s="14">
         <v>1</v>
       </c>
-      <c r="G62" s="19"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
+      <c r="G62" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E62,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H62" s="20">
+        <f>IFERROR(VLOOKUP(E62,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I62" s="20">
+        <f>IFERROR(F62*H62*(1-VLOOKUP(VLOOKUP(E62,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>56260</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
@@ -4909,9 +5621,18 @@
       <c r="F63" s="14">
         <v>4</v>
       </c>
-      <c r="G63" s="19"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
+      <c r="G63" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E63,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H63" s="20">
+        <f>IFERROR(VLOOKUP(E63,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I63" s="20">
+        <f>IFERROR(F63*H63*(1-VLOOKUP(VLOOKUP(E63,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>920000</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
@@ -4932,9 +5653,18 @@
       <c r="F64" s="14">
         <v>3</v>
       </c>
-      <c r="G64" s="19"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
+      <c r="G64" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E64,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H64" s="20">
+        <f>IFERROR(VLOOKUP(E64,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I64" s="20">
+        <f>IFERROR(F64*H64*(1-VLOOKUP(VLOOKUP(E64,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1904400</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
@@ -4955,9 +5685,18 @@
       <c r="F65" s="14">
         <v>6</v>
       </c>
-      <c r="G65" s="19"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
+      <c r="G65" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E65,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H65" s="20">
+        <f>IFERROR(VLOOKUP(E65,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I65" s="20">
+        <f>IFERROR(F65*H65*(1-VLOOKUP(VLOOKUP(E65,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>3808800</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
@@ -4978,9 +5717,18 @@
       <c r="F66" s="14">
         <v>3</v>
       </c>
-      <c r="G66" s="19"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
+      <c r="G66" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E66,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Disco SSD 1TB</v>
+      </c>
+      <c r="H66" s="20">
+        <f>IFERROR(VLOOKUP(E66,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>390000</v>
+      </c>
+      <c r="I66" s="20">
+        <f>IFERROR(F66*H66*(1-VLOOKUP(VLOOKUP(E66,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1134900</v>
+      </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
@@ -5001,9 +5749,18 @@
       <c r="F67" s="14">
         <v>4</v>
       </c>
-      <c r="G67" s="19"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
+      <c r="G67" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E67,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Monitor 24"</v>
+      </c>
+      <c r="H67" s="20">
+        <f>IFERROR(VLOOKUP(E67,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>690000</v>
+      </c>
+      <c r="I67" s="20">
+        <f>IFERROR(F67*H67*(1-VLOOKUP(VLOOKUP(E67,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>2539200</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
@@ -5024,9 +5781,18 @@
       <c r="F68" s="14">
         <v>4</v>
       </c>
-      <c r="G68" s="19"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
+      <c r="G68" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E68,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Base refrigerante</v>
+      </c>
+      <c r="H68" s="20">
+        <f>IFERROR(VLOOKUP(E68,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>89000</v>
+      </c>
+      <c r="I68" s="20">
+        <f>IFERROR(F68*H68*(1-VLOOKUP(VLOOKUP(E68,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>313280</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
@@ -5047,9 +5813,18 @@
       <c r="F69" s="14">
         <v>5</v>
       </c>
-      <c r="G69" s="19"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
+      <c r="G69" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E69,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Teclado mecánico</v>
+      </c>
+      <c r="H69" s="20">
+        <f>IFERROR(VLOOKUP(E69,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>185000</v>
+      </c>
+      <c r="I69" s="20">
+        <f>IFERROR(F69*H69*(1-VLOOKUP(VLOOKUP(E69,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>878750</v>
+      </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
@@ -5070,9 +5845,18 @@
       <c r="F70" s="14">
         <v>4</v>
       </c>
-      <c r="G70" s="19"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="G70" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E70,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Portátil 14"</v>
+      </c>
+      <c r="H70" s="20">
+        <f>IFERROR(VLOOKUP(E70,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>3200000</v>
+      </c>
+      <c r="I70" s="20">
+        <f>IFERROR(F70*H70*(1-VLOOKUP(VLOOKUP(E70,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>11520000</v>
+      </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
@@ -5093,9 +5877,18 @@
       <c r="F71" s="14">
         <v>4</v>
       </c>
-      <c r="G71" s="19"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
+      <c r="G71" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E71,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H71" s="20">
+        <f>IFERROR(VLOOKUP(E71,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I71" s="20">
+        <f>IFERROR(F71*H71*(1-VLOOKUP(VLOOKUP(E71,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>580000</v>
+      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
@@ -5116,9 +5909,18 @@
       <c r="F72" s="14">
         <v>1</v>
       </c>
-      <c r="G72" s="19"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
+      <c r="G72" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E72,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Disco SSD 1TB</v>
+      </c>
+      <c r="H72" s="20">
+        <f>IFERROR(VLOOKUP(E72,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>390000</v>
+      </c>
+      <c r="I72" s="20">
+        <f>IFERROR(F72*H72*(1-VLOOKUP(VLOOKUP(E72,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>378300</v>
+      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
@@ -5139,9 +5941,18 @@
       <c r="F73" s="14">
         <v>5</v>
       </c>
-      <c r="G73" s="19"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
+      <c r="G73" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E73,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H73" s="20">
+        <f>IFERROR(VLOOKUP(E73,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I73" s="20">
+        <f>IFERROR(F73*H73*(1-VLOOKUP(VLOOKUP(E73,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>281300</v>
+      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
@@ -5162,9 +5973,18 @@
       <c r="F74" s="14">
         <v>3</v>
       </c>
-      <c r="G74" s="19"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
+      <c r="G74" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E74,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Portátil 14"</v>
+      </c>
+      <c r="H74" s="20">
+        <f>IFERROR(VLOOKUP(E74,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>3200000</v>
+      </c>
+      <c r="I74" s="20">
+        <f>IFERROR(F74*H74*(1-VLOOKUP(VLOOKUP(E74,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>8640000</v>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
@@ -5185,9 +6005,18 @@
       <c r="F75" s="14">
         <v>4</v>
       </c>
-      <c r="G75" s="19"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="G75" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E75,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Memoria USB 128GB</v>
+      </c>
+      <c r="H75" s="20">
+        <f>IFERROR(VLOOKUP(E75,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>58000</v>
+      </c>
+      <c r="I75" s="20">
+        <f>IFERROR(F75*H75*(1-VLOOKUP(VLOOKUP(E75,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>225040</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
@@ -5208,9 +6037,18 @@
       <c r="F76" s="14">
         <v>1</v>
       </c>
-      <c r="G76" s="19"/>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
+      <c r="G76" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E76,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Mouse inalámbrico</v>
+      </c>
+      <c r="H76" s="20">
+        <f>IFERROR(VLOOKUP(E76,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>72000</v>
+      </c>
+      <c r="I76" s="20">
+        <f>IFERROR(F76*H76*(1-VLOOKUP(VLOOKUP(E76,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>68400</v>
+      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
@@ -5231,9 +6069,18 @@
       <c r="F77" s="14">
         <v>1</v>
       </c>
-      <c r="G77" s="19"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
+      <c r="G77" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E77,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H77" s="20">
+        <f>IFERROR(VLOOKUP(E77,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I77" s="20">
+        <f>IFERROR(F77*H77*(1-VLOOKUP(VLOOKUP(E77,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>230000</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
@@ -5254,9 +6101,18 @@
       <c r="F78" s="14">
         <v>6</v>
       </c>
-      <c r="G78" s="19"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
+      <c r="G78" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E78,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Mouse inalámbrico</v>
+      </c>
+      <c r="H78" s="20">
+        <f>IFERROR(VLOOKUP(E78,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>72000</v>
+      </c>
+      <c r="I78" s="20">
+        <f>IFERROR(F78*H78*(1-VLOOKUP(VLOOKUP(E78,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>410400</v>
+      </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
@@ -5277,9 +6133,18 @@
       <c r="F79" s="14">
         <v>5</v>
       </c>
-      <c r="G79" s="19"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
+      <c r="G79" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E79,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Portátil 16"</v>
+      </c>
+      <c r="H79" s="20">
+        <f>IFERROR(VLOOKUP(E79,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>4550000</v>
+      </c>
+      <c r="I79" s="20">
+        <f>IFERROR(F79*H79*(1-VLOOKUP(VLOOKUP(E79,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>20475000</v>
+      </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
@@ -5300,9 +6165,18 @@
       <c r="F80" s="14">
         <v>3</v>
       </c>
-      <c r="G80" s="19"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
+      <c r="G80" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E80,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Base refrigerante</v>
+      </c>
+      <c r="H80" s="20">
+        <f>IFERROR(VLOOKUP(E80,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>89000</v>
+      </c>
+      <c r="I80" s="20">
+        <f>IFERROR(F80*H80*(1-VLOOKUP(VLOOKUP(E80,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>234960</v>
+      </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
@@ -5323,9 +6197,18 @@
       <c r="F81" s="14">
         <v>4</v>
       </c>
-      <c r="G81" s="19"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
+      <c r="G81" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E81,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Teclado mecánico</v>
+      </c>
+      <c r="H81" s="20">
+        <f>IFERROR(VLOOKUP(E81,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>185000</v>
+      </c>
+      <c r="I81" s="20">
+        <f>IFERROR(F81*H81*(1-VLOOKUP(VLOOKUP(E81,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>703000</v>
+      </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
@@ -5346,9 +6229,18 @@
       <c r="F82" s="14">
         <v>6</v>
       </c>
-      <c r="G82" s="19"/>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
+      <c r="G82" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E82,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Diadema USB</v>
+      </c>
+      <c r="H82" s="20">
+        <f>IFERROR(VLOOKUP(E82,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>145000</v>
+      </c>
+      <c r="I82" s="20">
+        <f>IFERROR(F82*H82*(1-VLOOKUP(VLOOKUP(E82,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>870000</v>
+      </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
@@ -5369,9 +6261,18 @@
       <c r="F83" s="14">
         <v>6</v>
       </c>
-      <c r="G83" s="19"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
+      <c r="G83" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E83,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Parlantes 2.1</v>
+      </c>
+      <c r="H83" s="20">
+        <f>IFERROR(VLOOKUP(E83,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>230000</v>
+      </c>
+      <c r="I83" s="20">
+        <f>IFERROR(F83*H83*(1-VLOOKUP(VLOOKUP(E83,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1380000</v>
+      </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
@@ -5392,9 +6293,18 @@
       <c r="F84" s="14">
         <v>6</v>
       </c>
-      <c r="G84" s="19"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
+      <c r="G84" s="19" t="str">
+        <f>IFERROR(VLOOKUP(E84,Catálogo!$A$5:$B$16,2,FALSE),"CÓDIGO NO EXISTE")</f>
+        <v>Teclado mecánico</v>
+      </c>
+      <c r="H84" s="20">
+        <f>IFERROR(VLOOKUP(E84,Catálogo!$A$5:$D$16,4,FALSE),0)</f>
+        <v>185000</v>
+      </c>
+      <c r="I84" s="20">
+        <f>IFERROR(F84*H84*(1-VLOOKUP(VLOOKUP(E84,Catálogo!$A$5:$C$16,3,FALSE),Catálogo!$I$6:$J$11,2,FALSE)),0)</f>
+        <v>1054500</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5481,65 +6391,182 @@
       <c r="A5" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="23"/>
+      <c r="B5" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A5,Ventas!$B$5:$B$84,"&gt;="&amp;B$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>33499800</v>
+      </c>
+      <c r="C5" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A5,Ventas!$B$5:$B$84,"&gt;="&amp;C$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>3596550</v>
+      </c>
+      <c r="D5" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A5,Ventas!$B$5:$B$84,"&gt;="&amp;D$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>2076650</v>
+      </c>
+      <c r="E5" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A5,Ventas!$B$5:$B$84,"&gt;="&amp;E$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>7608400</v>
+      </c>
+      <c r="F5" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A5,Ventas!$B$5:$B$84,"&gt;="&amp;F$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>3794950</v>
+      </c>
+      <c r="G5" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A5,Ventas!$B$5:$B$84,"&gt;="&amp;G$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>4062900</v>
+      </c>
+      <c r="H5" s="20">
+        <f>SUM(B5:G5)</f>
+        <v>54639250</v>
+      </c>
+      <c r="I5" s="23">
+        <f>H5/$H$9</f>
+        <v>0.40657722093065046</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="23"/>
+      <c r="B6" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A6,Ventas!$B$5:$B$84,"&gt;="&amp;B$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>4409240</v>
+      </c>
+      <c r="C6" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A6,Ventas!$B$5:$B$84,"&gt;="&amp;C$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>1282500</v>
+      </c>
+      <c r="D6" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A6,Ventas!$B$5:$B$84,"&gt;="&amp;D$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>2294120</v>
+      </c>
+      <c r="E6" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A6,Ventas!$B$5:$B$84,"&gt;="&amp;E$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>205200</v>
+      </c>
+      <c r="F6" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A6,Ventas!$B$5:$B$84,"&gt;="&amp;F$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>11898300</v>
+      </c>
+      <c r="G6" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A6,Ventas!$B$5:$B$84,"&gt;="&amp;G$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>9343000</v>
+      </c>
+      <c r="H6" s="20">
+        <f t="shared" ref="H6:H14" si="0">SUM(B6:G6)</f>
+        <v>29432360</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" ref="I6:I8" si="1">H6/$H$9</f>
+        <v>0.2190097253207253</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="23"/>
+      <c r="B7" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A7,Ventas!$B$5:$B$84,"&gt;="&amp;B$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A7,Ventas!$B$5:$B$84,"&gt;="&amp;C$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>3808800</v>
+      </c>
+      <c r="D7" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A7,Ventas!$B$5:$B$84,"&gt;="&amp;D$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>1614960</v>
+      </c>
+      <c r="E7" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A7,Ventas!$B$5:$B$84,"&gt;="&amp;E$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>6966260</v>
+      </c>
+      <c r="F7" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A7,Ventas!$B$5:$B$84,"&gt;="&amp;F$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>8722430</v>
+      </c>
+      <c r="G7" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A7,Ventas!$B$5:$B$84,"&gt;="&amp;G$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>20885400</v>
+      </c>
+      <c r="H7" s="20">
+        <f t="shared" si="0"/>
+        <v>41997850</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="1"/>
+        <v>0.31251104541263502</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="23"/>
+      <c r="B8" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A8,Ventas!$B$5:$B$84,"&gt;="&amp;B$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>1216310</v>
+      </c>
+      <c r="C8" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A8,Ventas!$B$5:$B$84,"&gt;="&amp;C$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>4192560</v>
+      </c>
+      <c r="D8" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A8,Ventas!$B$5:$B$84,"&gt;="&amp;D$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>1630500</v>
+      </c>
+      <c r="E8" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A8,Ventas!$B$5:$B$84,"&gt;="&amp;E$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>1223280</v>
+      </c>
+      <c r="F8" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A8,Ventas!$B$5:$B$84,"&gt;="&amp;F$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>56260</v>
+      </c>
+      <c r="G8" s="20">
+        <f>SUMIFS(Ventas!$I$5:$I$84,Ventas!$D$5:$D$84,$A8,Ventas!$B$5:$B$84,"&gt;="&amp;G$4,Ventas!$B$5:$B$84,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="20">
+        <f t="shared" si="0"/>
+        <v>8318910</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="1"/>
+        <v>6.1902008335989196E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+      <c r="B9" s="20">
+        <f>SUM(B5:B8)</f>
+        <v>39125350</v>
+      </c>
+      <c r="C9" s="20">
+        <f t="shared" ref="C9:H9" si="2">SUM(C5:C8)</f>
+        <v>12880410</v>
+      </c>
+      <c r="D9" s="20">
+        <f t="shared" si="2"/>
+        <v>7616230</v>
+      </c>
+      <c r="E9" s="20">
+        <f t="shared" si="2"/>
+        <v>16003140</v>
+      </c>
+      <c r="F9" s="20">
+        <f t="shared" si="2"/>
+        <v>24471940</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="2"/>
+        <v>34291300</v>
+      </c>
+      <c r="H9" s="20">
+        <f t="shared" si="2"/>
+        <v>134388370</v>
+      </c>
       <c r="I9" s="2"/>
     </row>
   </sheetData>
@@ -5654,10 +6681,22 @@
       <c r="A6" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="24"/>
+      <c r="B6" s="20">
+        <f>SUMIF(Ventas!$C$5:$C$84,$A6,Ventas!$I$5:$I$84)</f>
+        <v>36026260</v>
+      </c>
+      <c r="C6" s="23">
+        <f>VLOOKUP(B6,$J$7:$K$11,2,TRUE)</f>
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="20">
+        <f>B6*C6</f>
+        <v>1801313</v>
+      </c>
+      <c r="E6" s="24" t="b">
+        <f>(SUMIFS(Ventas!$I$5:$I$84,Ventas!$C$5:$C$84,$A6,Ventas!$B$5:$B$84,"&gt;="&amp;DATE(2026,1,1),Ventas!$B$5:$B$84,"&lt;"&amp;DATE(2026,2,1))&gt;$C$3)</f>
+        <v>1</v>
+      </c>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="2"/>
@@ -5673,10 +6712,22 @@
       <c r="A7" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="24"/>
+      <c r="B7" s="20">
+        <f>SUMIF(Ventas!$C$5:$C$84,$A7,Ventas!$I$5:$I$84)</f>
+        <v>29432360</v>
+      </c>
+      <c r="C7" s="23">
+        <f t="shared" ref="C7:C10" si="0">VLOOKUP(B7,$J$7:$K$11,2,TRUE)</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D7" s="20">
+        <f t="shared" ref="D7:D10" si="1">B7*C7</f>
+        <v>1030132.6000000001</v>
+      </c>
+      <c r="E7" s="24" t="b">
+        <f>(SUMIFS(Ventas!$I$5:$I$84,Ventas!$C$5:$C$84,$A7,Ventas!$B$5:$B$84,"&gt;="&amp;DATE(2026,1,1),Ventas!$B$5:$B$84,"&lt;"&amp;DATE(2026,2,1))&gt;$C$3)</f>
+        <v>1</v>
+      </c>
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
       <c r="H7" s="2"/>
@@ -5692,10 +6743,22 @@
       <c r="A8" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="24"/>
+      <c r="B8" s="20">
+        <f>SUMIF(Ventas!$C$5:$C$84,$A8,Ventas!$I$5:$I$84)</f>
+        <v>41997850</v>
+      </c>
+      <c r="C8" s="23">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="20">
+        <f t="shared" si="1"/>
+        <v>2099892.5</v>
+      </c>
+      <c r="E8" s="24" t="b">
+        <f>(SUMIFS(Ventas!$I$5:$I$84,Ventas!$C$5:$C$84,$A8,Ventas!$B$5:$B$84,"&gt;="&amp;DATE(2026,1,1),Ventas!$B$5:$B$84,"&lt;"&amp;DATE(2026,2,1))&gt;$C$3)</f>
+        <v>0</v>
+      </c>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
       <c r="H8" s="2"/>
@@ -5711,10 +6774,22 @@
       <c r="A9" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="24"/>
+      <c r="B9" s="20">
+        <f>SUMIF(Ventas!$C$5:$C$84,$A9,Ventas!$I$5:$I$84)</f>
+        <v>18032990</v>
+      </c>
+      <c r="C9" s="23">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="20">
+        <f t="shared" si="1"/>
+        <v>360659.8</v>
+      </c>
+      <c r="E9" s="24" t="b">
+        <f>(SUMIFS(Ventas!$I$5:$I$84,Ventas!$C$5:$C$84,$A9,Ventas!$B$5:$B$84,"&gt;="&amp;DATE(2026,1,1),Ventas!$B$5:$B$84,"&lt;"&amp;DATE(2026,2,1))&gt;$C$3)</f>
+        <v>1</v>
+      </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="2"/>
@@ -5730,10 +6805,22 @@
       <c r="A10" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="24"/>
+      <c r="B10" s="20">
+        <f>SUMIF(Ventas!$C$5:$C$84,$A10,Ventas!$I$5:$I$84)</f>
+        <v>8318910</v>
+      </c>
+      <c r="C10" s="23">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="D10" s="20">
+        <f t="shared" si="1"/>
+        <v>83189.100000000006</v>
+      </c>
+      <c r="E10" s="24" t="b">
+        <f>(SUMIFS(Ventas!$I$5:$I$84,Ventas!$C$5:$C$84,$A10,Ventas!$B$5:$B$84,"&gt;="&amp;DATE(2026,1,1),Ventas!$B$5:$B$84,"&lt;"&amp;DATE(2026,2,1))&gt;$C$3)</f>
+        <v>0</v>
+      </c>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
       <c r="H10" s="2"/>
@@ -5865,10 +6952,22 @@
       <c r="D6" s="15">
         <v>3800000</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="27"/>
+      <c r="E6" s="19" t="str">
+        <f>IF(DATEDIF(C6,$B$3,"y")=0,DATEDIF(C6,$B$3,"ym")&amp;" meses",DATEDIF(C6,$B$3,"y")&amp;" años y "&amp;DATEDIF(C6,$B$3,"ym")&amp;" meses")</f>
+        <v>4 años y 7 meses</v>
+      </c>
+      <c r="F6" s="26">
+        <f>IF(DATEDIF(C6,$B$3,"y")&lt;2,0,IF(DATEDIF(C6,$B$3,"y")&lt;5,0.05,IF(DATEDIF(C6,$B$3,"y")&lt;10,0.1,0.15)))</f>
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="20">
+        <f>D6*F6</f>
+        <v>190000</v>
+      </c>
+      <c r="H6" s="27">
+        <f>DATE(YEAR($B$3)+IF(DATE(YEAR($B$3),MONTH(C6),DAY(C6))&lt;=$B$3,1,0),MONTH(C6),DAY(C6))</f>
+        <v>46341</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -5883,10 +6982,22 @@
       <c r="D7" s="15">
         <v>6200000</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="27"/>
+      <c r="E7" s="19" t="str">
+        <f t="shared" ref="E7:E15" si="0">IF(DATEDIF(C7,$B$3,"y")=0,DATEDIF(C7,$B$3,"ym")&amp;" meses",DATEDIF(C7,$B$3,"y")&amp;" años y "&amp;DATEDIF(C7,$B$3,"ym")&amp;" meses")</f>
+        <v>12 años y 3 meses</v>
+      </c>
+      <c r="F7" s="26">
+        <f t="shared" ref="F7:F15" si="1">IF(DATEDIF(C7,$B$3,"y")&lt;2,0,IF(DATEDIF(C7,$B$3,"y")&lt;5,0.05,IF(DATEDIF(C7,$B$3,"y")&lt;10,0.1,0.15)))</f>
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="20">
+        <f t="shared" ref="G7:G15" si="2">D7*F7</f>
+        <v>930000</v>
+      </c>
+      <c r="H7" s="27">
+        <f t="shared" ref="H7:H15" si="3">DATE(YEAR($B$3)+IF(DATE(YEAR($B$3),MONTH(C7),DAY(C7))&lt;=$B$3,1,0),MONTH(C7),DAY(C7))</f>
+        <v>46448</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
@@ -5901,10 +7012,22 @@
       <c r="D8" s="15">
         <v>1900000</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="27"/>
+      <c r="E8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>6 meses</v>
+      </c>
+      <c r="F8" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="27">
+        <f t="shared" si="3"/>
+        <v>46357</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
@@ -5919,10 +7042,22 @@
       <c r="D9" s="15">
         <v>5400000</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="27"/>
+      <c r="E9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>7 años y 0 meses</v>
+      </c>
+      <c r="F9" s="26">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="2"/>
+        <v>540000</v>
+      </c>
+      <c r="H9" s="27">
+        <f t="shared" si="3"/>
+        <v>46568</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -5937,10 +7072,22 @@
       <c r="D10" s="15">
         <v>11500000</v>
       </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="27"/>
+      <c r="E10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>17 años y 10 meses</v>
+      </c>
+      <c r="F10" s="26">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="20">
+        <f t="shared" si="2"/>
+        <v>1725000</v>
+      </c>
+      <c r="H10" s="27">
+        <f t="shared" si="3"/>
+        <v>46254</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
@@ -5955,10 +7102,22 @@
       <c r="D11" s="15">
         <v>3600000</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="27"/>
+      <c r="E11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>2 años y 4 meses</v>
+      </c>
+      <c r="F11" s="26">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="20">
+        <f t="shared" si="2"/>
+        <v>180000</v>
+      </c>
+      <c r="H11" s="27">
+        <f t="shared" si="3"/>
+        <v>46447</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
@@ -5973,10 +7132,22 @@
       <c r="D12" s="15">
         <v>4700000</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="27"/>
+      <c r="E12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>9 años y 11 meses</v>
+      </c>
+      <c r="F12" s="26">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="20">
+        <f t="shared" si="2"/>
+        <v>470000</v>
+      </c>
+      <c r="H12" s="27">
+        <f t="shared" si="3"/>
+        <v>46204</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
@@ -5991,10 +7162,22 @@
       <c r="D13" s="15">
         <v>1950000</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="27"/>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>3 años y 0 meses</v>
+      </c>
+      <c r="F13" s="26">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="20">
+        <f t="shared" si="2"/>
+        <v>97500</v>
+      </c>
+      <c r="H13" s="27">
+        <f t="shared" si="3"/>
+        <v>46568</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
@@ -6009,10 +7192,22 @@
       <c r="D14" s="15">
         <v>7300000</v>
       </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="27"/>
+      <c r="E14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>15 años y 5 meses</v>
+      </c>
+      <c r="F14" s="26">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+      <c r="G14" s="20">
+        <f t="shared" si="2"/>
+        <v>1095000</v>
+      </c>
+      <c r="H14" s="27">
+        <f t="shared" si="3"/>
+        <v>46397</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
@@ -6027,10 +7222,22 @@
       <c r="D15" s="15">
         <v>5900000</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="27"/>
+      <c r="E15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>5 años y 0 meses</v>
+      </c>
+      <c r="F15" s="26">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="20">
+        <f t="shared" si="2"/>
+        <v>590000</v>
+      </c>
+      <c r="H15" s="27">
+        <f t="shared" si="3"/>
+        <v>46567</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6125,12 +7332,30 @@
       <c r="C5" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
+      <c r="D5" s="19" t="str">
+        <f>PROPER(TRIM(A5))</f>
+        <v>Juan Pérez Gómez</v>
+      </c>
+      <c r="E5" s="19" t="str">
+        <f>MID(D5&amp;" ",FIND(" ",D5&amp;" ")+1,FIND(" ",D5&amp;" ",FIND(" ",D5&amp;" ")+1)-FIND(" ",D5&amp;" ")-1)</f>
+        <v>Pérez</v>
+      </c>
+      <c r="F5" s="19" t="str">
+        <f>LEFT(TRIM(B5),FIND("@",TRIM(B5))-1)</f>
+        <v>juan.perez</v>
+      </c>
+      <c r="G5" s="19" t="str">
+        <f>LOWER(MID(TRIM(B5),FIND("@",TRIM(B5))+1,100))</f>
+        <v>gmail.com</v>
+      </c>
+      <c r="H5" s="19" t="str">
+        <f>RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"-",""),"(",""),")",""),"+",""),".",""),10)</f>
+        <v>3001234567</v>
+      </c>
+      <c r="I5" s="19" t="str">
+        <f>IF(SUMPRODUCT(--(LOWER(TRIM($B$5:$B$16))=LOWER(TRIM(B5))))&gt;1,"SÍ","")</f>
+        <v>SÍ</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
@@ -6142,12 +7367,30 @@
       <c r="C6" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
+      <c r="D6" s="19" t="str">
+        <f t="shared" ref="D6:D16" si="0">PROPER(TRIM(A6))</f>
+        <v>María Fernanda López</v>
+      </c>
+      <c r="E6" s="19" t="str">
+        <f t="shared" ref="E6:E16" si="1">MID(D6&amp;" ",FIND(" ",D6&amp;" ")+1,FIND(" ",D6&amp;" ",FIND(" ",D6&amp;" ")+1)-FIND(" ",D6&amp;" ")-1)</f>
+        <v>Fernanda</v>
+      </c>
+      <c r="F6" s="19" t="str">
+        <f t="shared" ref="F6:F16" si="2">LEFT(TRIM(B6),FIND("@",TRIM(B6))-1)</f>
+        <v>mfl88</v>
+      </c>
+      <c r="G6" s="19" t="str">
+        <f t="shared" ref="G6:G16" si="3">LOWER(MID(TRIM(B6),FIND("@",TRIM(B6))+1,100))</f>
+        <v>hotmail.com</v>
+      </c>
+      <c r="H6" s="19" t="str">
+        <f t="shared" ref="H6:H16" si="4">RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"-",""),"(",""),")",""),"+",""),".",""),10)</f>
+        <v>3105557788</v>
+      </c>
+      <c r="I6" s="19" t="str">
+        <f t="shared" ref="I6:I16" si="5">IF(SUMPRODUCT(--(LOWER(TRIM($B$5:$B$16))=LOWER(TRIM(B6))))&gt;1,"SÍ","")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -6159,12 +7402,30 @@
       <c r="C7" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+      <c r="D7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Carlos Andrés Ruiz</v>
+      </c>
+      <c r="E7" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Andrés</v>
+      </c>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>carlos.ruiz</v>
+      </c>
+      <c r="G7" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>empresa.co</v>
+      </c>
+      <c r="H7" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3152223344</v>
+      </c>
+      <c r="I7" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
@@ -6176,12 +7437,30 @@
       <c r="C8" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
+      <c r="D8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Ana Sofía Vélez</v>
+      </c>
+      <c r="E8" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Sofía</v>
+      </c>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>ANA.VELEZ</v>
+      </c>
+      <c r="G8" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>outlook.com</v>
+      </c>
+      <c r="H8" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3204445566</v>
+      </c>
+      <c r="I8" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>SÍ</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
@@ -6193,12 +7472,30 @@
       <c r="C9" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
+      <c r="D9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Pedro Ramírez</v>
+      </c>
+      <c r="E9" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramírez</v>
+      </c>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>pramirez</v>
+      </c>
+      <c r="G9" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>yahoo.es</v>
+      </c>
+      <c r="H9" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3019990000</v>
+      </c>
+      <c r="I9" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -6210,12 +7507,30 @@
       <c r="C10" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
+      <c r="D10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Juan Pérez Gómez</v>
+      </c>
+      <c r="E10" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pérez</v>
+      </c>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>JUAN.PEREZ</v>
+      </c>
+      <c r="G10" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>gmail.com</v>
+      </c>
+      <c r="H10" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3001234567</v>
+      </c>
+      <c r="I10" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>SÍ</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
@@ -6227,12 +7542,30 @@
       <c r="C11" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
+      <c r="D11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Lucía Martínez Ortiz</v>
+      </c>
+      <c r="E11" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Martínez</v>
+      </c>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>lucia_mo</v>
+      </c>
+      <c r="G11" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>gmail.com</v>
+      </c>
+      <c r="H11" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3118887766</v>
+      </c>
+      <c r="I11" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
@@ -6244,12 +7577,30 @@
       <c r="C12" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
+      <c r="D12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Jorge Eliécer Gaitán</v>
+      </c>
+      <c r="E12" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Eliécer</v>
+      </c>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>jegaitan</v>
+      </c>
+      <c r="G12" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>empresa.co</v>
+      </c>
+      <c r="H12" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3120001122</v>
+      </c>
+      <c r="I12" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
@@ -6261,12 +7612,30 @@
       <c r="C13" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+      <c r="D13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Valeria Cano</v>
+      </c>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Cano</v>
+      </c>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>vcano</v>
+      </c>
+      <c r="G13" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>hotmail.com</v>
+      </c>
+      <c r="H13" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3167778899</v>
+      </c>
+      <c r="I13" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
@@ -6278,12 +7647,30 @@
       <c r="C14" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
+      <c r="D14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Ana Sofía Vélez</v>
+      </c>
+      <c r="E14" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Sofía</v>
+      </c>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>ana.velez</v>
+      </c>
+      <c r="G14" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>outlook.com</v>
+      </c>
+      <c r="H14" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3204445566</v>
+      </c>
+      <c r="I14" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>SÍ</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
@@ -6295,12 +7682,30 @@
       <c r="C15" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
+      <c r="D15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Diego Alejandro Mesa</v>
+      </c>
+      <c r="E15" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Alejandro</v>
+      </c>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>dmesa</v>
+      </c>
+      <c r="G15" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>unal.edu.co</v>
+      </c>
+      <c r="H15" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3175550011</v>
+      </c>
+      <c r="I15" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
@@ -6312,12 +7717,30 @@
       <c r="C16" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
+      <c r="D16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>Paula Andrea Quintero</v>
+      </c>
+      <c r="E16" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>Andrea</v>
+      </c>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>pquintero</v>
+      </c>
+      <c r="G16" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>gmail.com</v>
+      </c>
+      <c r="H16" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>3007654321</v>
+      </c>
+      <c r="I16" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6395,43 +7818,73 @@
       <c r="A5" s="22">
         <v>1</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="19" t="e">
+        <f>INDEX(E3_Comisiones!$A$6:$A$10,MATCH(1,(E3_Comisiones!$B$6:$B$10=C5)*(COUNTIF($B$4:B4,E3_Comisiones!$A$6:$A$10)=0),0))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="20">
+        <f>LARGE(E3_Comisiones!$B$6:$B$10,A5)</f>
+        <v>41997850</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="22">
         <v>1</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="G5" s="19" t="e">
+        <f>INDEX(Catálogo!$B$5:$B$16,MATCH(1,(SUMIF(Ventas!$E$5:$E$84,Catálogo!$A$5:$A$16,Ventas!$F$5:$F$84)=H5)*(COUNTIF($G$4:G4,Catálogo!$B$5:$B$16)=0),0))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H5" s="19">
+        <f>LARGE(SUMIF(Ventas!$E$5:$E$84,Catálogo!$A$5:$A$16,Ventas!$F$5:$F$84),F5)</f>
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>2</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20"/>
+      <c r="B6" s="19" t="e">
+        <f>INDEX(E3_Comisiones!$A$6:$A$10,MATCH(1,(E3_Comisiones!$B$6:$B$10=C6)*(COUNTIF($B$4:B5,E3_Comisiones!$A$6:$A$10)=0),0))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C6" s="20">
+        <f>LARGE(E3_Comisiones!$B$6:$B$10,A6)</f>
+        <v>36026260</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="22">
         <v>2</v>
       </c>
       <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="H6" s="19" t="e">
+        <f>LARGE(SUMIF(Ventas!$E$5:$E$84,Catálogo!$A$5:$A$16,Ventas!$F$5:$F$84),F6)</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <v>3</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
+      <c r="B7" s="19" t="e">
+        <f>INDEX(E3_Comisiones!$A$6:$A$10,MATCH(1,(E3_Comisiones!$B$6:$B$10=C7)*(COUNTIF($B$4:B6,E3_Comisiones!$A$6:$A$10)=0),0))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C7" s="20">
+        <f>LARGE(E3_Comisiones!$B$6:$B$10,A7)</f>
+        <v>29432360</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="22">
         <v>3</v>
       </c>
       <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="H7" s="19" t="e">
+        <f>LARGE(SUMIF(Ventas!$E$5:$E$84,Catálogo!$A$5:$A$16,Ventas!$F$5:$F$84),F7)</f>
+        <v>#NUM!</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
